--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -640,25 +640,25 @@
     <t>10025301</t>
   </si>
   <si>
-    <t>QUAKER OAT MERAH 800</t>
+    <t>QUAKER OAT MRH 800 G</t>
   </si>
   <si>
     <t>20001605</t>
   </si>
   <si>
-    <t>ENRGEN CKLT PCK 10'S</t>
+    <t>ENERGEN CKLT 10X35 G</t>
   </si>
   <si>
     <t>20001604</t>
   </si>
   <si>
-    <t>ENRGEN VAN PCK 10'S</t>
+    <t>ENERGEN VAN  10X34 G</t>
   </si>
   <si>
     <t>20001606</t>
   </si>
   <si>
-    <t>ENERGEN KCNG.HJ 10'S</t>
+    <t>ENERGEN K.HJ 10X35 G</t>
   </si>
   <si>
     <t>10036853</t>
@@ -877,7 +877,7 @@
     <t>20136451</t>
   </si>
   <si>
-    <t>NSCAFE AMERICANO 10S</t>
+    <t>NESCAFE AMRCN 10X2 G</t>
   </si>
   <si>
     <t>20142007</t>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -316,13 +316,13 @@
     <t>10025006</t>
   </si>
   <si>
-    <t>NESTLE KOKO.COMBO 30</t>
+    <t>NESTLE KOKO CMB 30 G</t>
   </si>
   <si>
     <t>20032723</t>
   </si>
   <si>
-    <t>MILO CEREAL COKLT 30</t>
+    <t>MILO CEREAL CKT 30 G</t>
   </si>
   <si>
     <t>20113150</t>
@@ -334,13 +334,13 @@
     <t>20111959</t>
   </si>
   <si>
-    <t>KOKO KRNCH DB.CHO 30</t>
+    <t>NESTLE KK D CHO 30 G</t>
   </si>
   <si>
     <t>20046903</t>
   </si>
   <si>
-    <t>NESTLE HONY STAR 30G</t>
+    <t>NESTLE HNY STAR 30 G</t>
   </si>
   <si>
     <t>20136090</t>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -304,13 +304,13 @@
     <t>10011021</t>
   </si>
   <si>
-    <t>SIMBA CRL C/C COK 34</t>
+    <t>SIMBA CRL C COK 34 G</t>
   </si>
   <si>
     <t>10011020</t>
   </si>
   <si>
-    <t>SIMBA CRL C/C PTH 34</t>
+    <t>SIMBA CRL C PTH 34 G</t>
   </si>
   <si>
     <t>10025006</t>
@@ -328,7 +328,7 @@
     <t>20113150</t>
   </si>
   <si>
-    <t>SIMBA CRL CC STRW 34</t>
+    <t>SIMBA CRL C STW 34 G</t>
   </si>
   <si>
     <t>20111959</t>
@@ -736,19 +736,19 @@
     <t>20046081</t>
   </si>
   <si>
-    <t>G/D 3IN1 MCCINO 10'S</t>
+    <t>G/DAY MOCCA 10x20 G</t>
   </si>
   <si>
     <t>20060370</t>
   </si>
   <si>
-    <t>G/DAY CHOCOCINO 10'S</t>
+    <t>G/DAY CHOCCN 10x20 G</t>
   </si>
   <si>
     <t>20060371</t>
   </si>
   <si>
-    <t>G/DAY VNL.LATTE 10'S</t>
+    <t>G/DAY VNL.LT 10x20 G</t>
   </si>
   <si>
     <t>20100796</t>
@@ -862,7 +862,7 @@
     <t>20143384</t>
   </si>
   <si>
-    <t>K/A BLCK COFE SPR10S</t>
+    <t>K/A B.CFE S 10X2.2 G</t>
   </si>
   <si>
     <t>17</t>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -346,7 +346,7 @@
     <t>20136090</t>
   </si>
   <si>
-    <t>NESTLE TRIX CUP 30G</t>
+    <t>NSTL C/B TR CUP 30 G</t>
   </si>
   <si>
     <t>20137761</t>
